--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_reinsurance.xlsx
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.05769999999999999</v>
+        <v>0.0824</v>
       </c>
       <c r="E2">
-        <v>0.237</v>
+        <v>-0.0868</v>
       </c>
       <c r="G2">
-        <v>0.06180257510729614</v>
+        <v>0.06189710610932476</v>
       </c>
       <c r="H2">
-        <v>0.06180257510729614</v>
+        <v>0.06189710610932476</v>
       </c>
       <c r="I2">
-        <v>0.07682403433476394</v>
+        <v>0.07355305466237942</v>
       </c>
       <c r="J2">
-        <v>0.06604320299717828</v>
+        <v>0.05348858192794802</v>
       </c>
       <c r="K2">
-        <v>15.6</v>
+        <v>10.7</v>
       </c>
       <c r="L2">
-        <v>0.06695278969957082</v>
+        <v>0.0430064308681672</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -633,55 +633,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="V2">
-        <v>0.03553299492385787</v>
+        <v>0.03694581280788177</v>
       </c>
       <c r="W2">
-        <v>0.065</v>
+        <v>0.04181320828448613</v>
       </c>
       <c r="X2">
-        <v>0.08486335332681245</v>
+        <v>0.1197022421395447</v>
       </c>
       <c r="Y2">
-        <v>-0.01986335332681245</v>
+        <v>-0.07788903385505855</v>
       </c>
       <c r="Z2">
-        <v>1.022378236068451</v>
+        <v>0.9677168416958382</v>
       </c>
       <c r="AA2">
-        <v>0.06752113338456578</v>
+        <v>0.05176180157010295</v>
       </c>
       <c r="AB2">
-        <v>0.08258273840426819</v>
+        <v>0.1163721794838398</v>
       </c>
       <c r="AC2">
-        <v>-0.01506160501970241</v>
+        <v>-0.06461037791373682</v>
       </c>
       <c r="AD2">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="AG2">
-        <v>1.199999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="AH2">
-        <v>0.03714565004887586</v>
+        <v>0.04442483083259782</v>
       </c>
       <c r="AI2">
-        <v>0.05606787163408335</v>
+        <v>0.05416068866571018</v>
       </c>
       <c r="AJ2">
-        <v>0.003036437246963561</v>
+        <v>0.009454101860323267</v>
       </c>
       <c r="AK2">
-        <v>0.00466744457409568</v>
+        <v>0.0116191904047976</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -690,10 +690,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>0.8216216216216216</v>
+        <v>0.7947368421052632</v>
       </c>
       <c r="AP2">
-        <v>0.06486486486486483</v>
+        <v>0.1631578947368421</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Saudi Re for Cooperative Reinsurance Company (SASE:8200)</t>
+          <t>Saudi Reinsurance Company (SASE:8200)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,28 +713,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.05769999999999999</v>
+        <v>0.0824</v>
       </c>
       <c r="E3">
-        <v>0.237</v>
+        <v>-0.0868</v>
       </c>
       <c r="G3">
-        <v>0.06180257510729614</v>
+        <v>0.06189710610932476</v>
       </c>
       <c r="H3">
-        <v>0.06180257510729614</v>
+        <v>0.06189710610932476</v>
       </c>
       <c r="I3">
-        <v>0.07682403433476394</v>
+        <v>0.07355305466237942</v>
       </c>
       <c r="J3">
-        <v>0.06604320299717828</v>
+        <v>0.05348858192794802</v>
       </c>
       <c r="K3">
-        <v>15.6</v>
+        <v>10.7</v>
       </c>
       <c r="L3">
-        <v>0.06695278969957082</v>
+        <v>0.0430064308681672</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="V3">
-        <v>0.03553299492385787</v>
+        <v>0.03694581280788177</v>
       </c>
       <c r="W3">
-        <v>0.065</v>
+        <v>0.04181320828448613</v>
       </c>
       <c r="X3">
-        <v>0.08486335332681245</v>
+        <v>0.1197022421395447</v>
       </c>
       <c r="Y3">
-        <v>-0.01986335332681245</v>
+        <v>-0.07788903385505855</v>
       </c>
       <c r="Z3">
-        <v>1.022378236068451</v>
+        <v>0.9677168416958382</v>
       </c>
       <c r="AA3">
-        <v>0.06752113338456578</v>
+        <v>0.05176180157010295</v>
       </c>
       <c r="AB3">
-        <v>0.08258273840426819</v>
+        <v>0.1163721794838398</v>
       </c>
       <c r="AC3">
-        <v>-0.01506160501970241</v>
+        <v>-0.06461037791373682</v>
       </c>
       <c r="AD3">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="AG3">
-        <v>1.199999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="AH3">
-        <v>0.03714565004887586</v>
+        <v>0.04442483083259782</v>
       </c>
       <c r="AI3">
-        <v>0.05606787163408335</v>
+        <v>0.05416068866571018</v>
       </c>
       <c r="AJ3">
-        <v>0.003036437246963561</v>
+        <v>0.009454101860323267</v>
       </c>
       <c r="AK3">
-        <v>0.00466744457409568</v>
+        <v>0.0116191904047976</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -815,10 +815,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.8216216216216216</v>
+        <v>0.7947368421052632</v>
       </c>
       <c r="AP3">
-        <v>0.06486486486486483</v>
+        <v>0.1631578947368421</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_reinsurance.xlsx
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0824</v>
+        <v>0.0842</v>
       </c>
       <c r="E2">
-        <v>-0.0868</v>
+        <v>0.19</v>
       </c>
       <c r="G2">
-        <v>0.06189710610932476</v>
+        <v>0.07548608463591308</v>
       </c>
       <c r="H2">
-        <v>0.06189710610932476</v>
+        <v>0.07548608463591308</v>
       </c>
       <c r="I2">
-        <v>0.07355305466237942</v>
+        <v>0.1010293556995806</v>
       </c>
       <c r="J2">
-        <v>0.05348858192794802</v>
+        <v>0.07960809381440639</v>
       </c>
       <c r="K2">
-        <v>10.7</v>
+        <v>21</v>
       </c>
       <c r="L2">
-        <v>0.0430064308681672</v>
+        <v>0.08006099885627144</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -633,55 +633,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>12</v>
+        <v>12.7</v>
       </c>
       <c r="V2">
-        <v>0.03694581280788177</v>
+        <v>0.02843071412581151</v>
       </c>
       <c r="W2">
-        <v>0.04181320828448613</v>
+        <v>0.07963594994311718</v>
       </c>
       <c r="X2">
-        <v>0.1197022421395447</v>
+        <v>0.1007256102458029</v>
       </c>
       <c r="Y2">
-        <v>-0.07788903385505855</v>
+        <v>-0.02108966030268573</v>
       </c>
       <c r="Z2">
-        <v>0.9677168416958382</v>
+        <v>0.9831334332833583</v>
       </c>
       <c r="AA2">
-        <v>0.05176180157010295</v>
+        <v>0.07826537858890105</v>
       </c>
       <c r="AB2">
-        <v>0.1163721794838398</v>
+        <v>0.09879903522473209</v>
       </c>
       <c r="AC2">
-        <v>-0.06461037791373682</v>
+        <v>-0.02053365663583104</v>
       </c>
       <c r="AD2">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="AG2">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="AH2">
-        <v>0.04442483083259782</v>
+        <v>0.03290755574799741</v>
       </c>
       <c r="AI2">
-        <v>0.05416068866571018</v>
+        <v>0.0482080558198541</v>
       </c>
       <c r="AJ2">
-        <v>0.009454101860323267</v>
+        <v>0.005565449688334817</v>
       </c>
       <c r="AK2">
-        <v>0.0116191904047976</v>
+        <v>0.008261731658955716</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -690,10 +690,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>0.7947368421052632</v>
+        <v>0.5608856088560885</v>
       </c>
       <c r="AP2">
-        <v>0.1631578947368421</v>
+        <v>0.09225092250922509</v>
       </c>
     </row>
     <row r="3">
@@ -713,28 +713,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0824</v>
+        <v>0.0842</v>
       </c>
       <c r="E3">
-        <v>-0.0868</v>
+        <v>0.19</v>
       </c>
       <c r="G3">
-        <v>0.06189710610932476</v>
+        <v>0.07548608463591308</v>
       </c>
       <c r="H3">
-        <v>0.06189710610932476</v>
+        <v>0.07548608463591308</v>
       </c>
       <c r="I3">
-        <v>0.07355305466237942</v>
+        <v>0.1010293556995806</v>
       </c>
       <c r="J3">
-        <v>0.05348858192794802</v>
+        <v>0.07960809381440639</v>
       </c>
       <c r="K3">
-        <v>10.7</v>
+        <v>21</v>
       </c>
       <c r="L3">
-        <v>0.0430064308681672</v>
+        <v>0.08006099885627144</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>12</v>
+        <v>12.7</v>
       </c>
       <c r="V3">
-        <v>0.03694581280788177</v>
+        <v>0.02843071412581151</v>
       </c>
       <c r="W3">
-        <v>0.04181320828448613</v>
+        <v>0.07963594994311718</v>
       </c>
       <c r="X3">
-        <v>0.1197022421395447</v>
+        <v>0.1007256102458029</v>
       </c>
       <c r="Y3">
-        <v>-0.07788903385505855</v>
+        <v>-0.02108966030268573</v>
       </c>
       <c r="Z3">
-        <v>0.9677168416958382</v>
+        <v>0.9831334332833583</v>
       </c>
       <c r="AA3">
-        <v>0.05176180157010295</v>
+        <v>0.07826537858890105</v>
       </c>
       <c r="AB3">
-        <v>0.1163721794838398</v>
+        <v>0.09879903522473209</v>
       </c>
       <c r="AC3">
-        <v>-0.06461037791373682</v>
+        <v>-0.02053365663583104</v>
       </c>
       <c r="AD3">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="AG3">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="AH3">
-        <v>0.04442483083259782</v>
+        <v>0.03290755574799741</v>
       </c>
       <c r="AI3">
-        <v>0.05416068866571018</v>
+        <v>0.0482080558198541</v>
       </c>
       <c r="AJ3">
-        <v>0.009454101860323267</v>
+        <v>0.005565449688334817</v>
       </c>
       <c r="AK3">
-        <v>0.0116191904047976</v>
+        <v>0.008261731658955716</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -815,10 +815,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.7947368421052632</v>
+        <v>0.5608856088560885</v>
       </c>
       <c r="AP3">
-        <v>0.1631578947368421</v>
+        <v>0.09225092250922509</v>
       </c>
     </row>
   </sheetData>
